--- a/result_gsea/LUAD_FAT1_chip/LUAD_MSigDB_Hallmark_2020/LUAD_GSEA_MSigDB_Hallmark_2020_results.xlsx
+++ b/result_gsea/LUAD_FAT1_chip/LUAD_MSigDB_Hallmark_2020/LUAD_GSEA_MSigDB_Hallmark_2020_results.xlsx
@@ -492,19 +492,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6549253163157486</v>
+        <v>0.6549253163157481</v>
       </c>
       <c r="D2" t="n">
-        <v>2.114567143177708</v>
+        <v>2.19170305431078</v>
       </c>
       <c r="E2" t="n">
         <v>0.001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1195660907995179</v>
+        <v>0.06453452841719291</v>
       </c>
       <c r="G2" t="n">
-        <v>0.033</v>
+        <v>0.017</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -534,19 +534,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.644304363614672</v>
+        <v>0.6443043636146721</v>
       </c>
       <c r="D3" t="n">
-        <v>2.105334248456161</v>
+        <v>2.133747556097465</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001</v>
+        <v>0.002016129032258064</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06267577340297309</v>
+        <v>0.05671216133632104</v>
       </c>
       <c r="G3" t="n">
-        <v>0.035</v>
+        <v>0.027</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -576,19 +576,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6310748270286449</v>
+        <v>0.6310748270286444</v>
       </c>
       <c r="D4" t="n">
-        <v>2.004560292902983</v>
+        <v>2.077275741314538</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001</v>
+        <v>0.00196078431372549</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09449578143832865</v>
+        <v>0.06518639234059891</v>
       </c>
       <c r="G4" t="n">
-        <v>0.065</v>
+        <v>0.045</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -618,19 +618,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5165764605723908</v>
+        <v>0.5165764605723905</v>
       </c>
       <c r="D5" t="n">
-        <v>2.001407733333037</v>
+        <v>2.037440868991503</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007751937984496124</v>
+        <v>0.001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07328244274809161</v>
+        <v>0.07186799755551029</v>
       </c>
       <c r="G5" t="n">
-        <v>0.067</v>
+        <v>0.062</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.5222121139430436</v>
+        <v>0.5222121139430435</v>
       </c>
       <c r="D6" t="n">
-        <v>1.979761404947235</v>
+        <v>2.030883948374496</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003968253968253968</v>
+        <v>0.006211180124223602</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07058256327842506</v>
+        <v>0.06023222652271339</v>
       </c>
       <c r="G6" t="n">
-        <v>0.077</v>
+        <v>0.064</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -702,19 +702,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.510846393550812</v>
+        <v>0.5108463935508111</v>
       </c>
       <c r="D7" t="n">
-        <v>1.935419278513043</v>
+        <v>1.9736271774424</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002016129032258064</v>
+        <v>0.006237006237006237</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08806749698674167</v>
+        <v>0.07529028315339173</v>
       </c>
       <c r="G7" t="n">
-        <v>0.108</v>
+        <v>0.092</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -744,19 +744,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6452596122441973</v>
+        <v>0.6452596122441961</v>
       </c>
       <c r="D8" t="n">
-        <v>1.912510638449261</v>
+        <v>1.966902391638695</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09063881076737645</v>
+        <v>0.06788697145185228</v>
       </c>
       <c r="G8" t="n">
-        <v>0.122</v>
+        <v>0.095</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -786,19 +786,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6714317932346008</v>
+        <v>0.6714317932346009</v>
       </c>
       <c r="D9" t="n">
-        <v>1.865105542976163</v>
+        <v>1.908702486258856</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01622718052738337</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1104057854560064</v>
+        <v>0.09020167040130374</v>
       </c>
       <c r="G9" t="n">
-        <v>0.156</v>
+        <v>0.125</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -824,37 +824,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Protein Secretion</t>
+          <t>Angiogenesis</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.494630769664671</v>
+        <v>0.6060980353037854</v>
       </c>
       <c r="D10" t="n">
-        <v>1.807538003754318</v>
+        <v>1.852283150820816</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02669404517453799</v>
+        <v>0.009881422924901186</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1444221240123209</v>
+        <v>0.116031778366266</v>
       </c>
       <c r="G10" t="n">
-        <v>0.198</v>
+        <v>0.167</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>55/96</t>
+          <t>16/36</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>34.23%</t>
+          <t>10.85%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>GOLGA4;IGF2R;CLCN3;SEC24D;ADAM10;GBF1;ARFGEF2;DST;TSPAN8;MON2;DNM1L;ATP1A1;KIF1B;ABCA1;DOP1A;SSPN;OCRL;LMAN1;COG2;AP3B1;VPS4B;RPS6KA3;ATP7A;M6PR;AP1G1;ARFGEF1;SCAMP1;STAM;SEC31A;EGFR;USO1;SH3GL2;SNAP23;RAB22A;YIPF6;TMX1;RAB14;SCRN1;STX7;ZW10;GALC;COPB2;RAB5A;AP2B1;ARFGAP3;ARFIP1;TMED10;SGMS1;COPB1;MAPK1;ANP32E;TMED2;PAM;ARCN1;CLTC</t>
+          <t>COL5A2;VCAN;STC1;JAG1;POSTN;FGFR1;COL3A1;VAV2;TNFRSF21;ITGAV;THBD;FSTL1;SERPINA5;CCND2;MSX1;PDGFA</t>
         </is>
       </c>
     </row>
@@ -866,37 +866,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IL-2/STAT5 Signaling</t>
+          <t>Protein Secretion</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.4944341147449108</v>
+        <v>0.4946307696646738</v>
       </c>
       <c r="D11" t="n">
-        <v>1.769973203285078</v>
+        <v>1.838096491205718</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02464065708418891</v>
+        <v>0.03099173553719008</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1608356769787063</v>
+        <v>0.1138154410266857</v>
       </c>
       <c r="G11" t="n">
-        <v>0.229</v>
+        <v>0.174</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>76/198</t>
+          <t>55/96</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>19.90%</t>
+          <t>34.23%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MYO1E;HIPK2;ITGA6;TNFSF11;ADAM19;UCK2;IL1R2;CDCP1;LIF;IGF1R;POU2F1;IGF2R;PHLDA1;HUWE1;AHNAK;BCL2;NCOA3;SYT11;IL18R1;RORA;FURIN;HK2;IRF6;BMPR2;ENPP1;SLC2A3;GABARAPL1;MXD1;PLEC;TNFRSF21;ITGAV;CYFIP1;LCLAT1;CKAP4;BMP2;TWSG1;SNX9;EMP1;MYC;PNP;NCS1;F2RL2;CCND2;COL6A1;PTCH1;ODC1;SPRY4;ITIH5;IKZF4;PRKCH;SCN9A;TIAM1;CDC6;RHOH;CASP3;MAFF;PLAGL1;SWAP70;DENND5A;ABCB1;P4HA1;RGS16;IL2RA;IL2RB;ETFBKMT;KLF6;TGM2;CA2;IKZF2;CD44;SELP;GBP4;LRIG1;SPRED2;IL4R;NOP2</t>
+          <t>GOLGA4;IGF2R;CLCN3;SEC24D;ADAM10;GBF1;ARFGEF2;DST;TSPAN8;MON2;DNM1L;ATP1A1;KIF1B;ABCA1;DOP1A;SSPN;OCRL;LMAN1;COG2;AP3B1;VPS4B;RPS6KA3;ATP7A;M6PR;AP1G1;ARFGEF1;SCAMP1;STAM;SEC31A;EGFR;USO1;SH3GL2;SNAP23;RAB22A;YIPF6;TMX1;RAB14;SCRN1;STX7;ZW10;GALC;COPB2;RAB5A;AP2B1;ARFGAP3;ARFIP1;TMED10;SGMS1;COPB1;MAPK1;ANP32E;TMED2;PAM;ARCN1;CLTC</t>
         </is>
       </c>
     </row>
@@ -908,37 +908,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Notch Signaling</t>
+          <t>IL-2/STAT5 Signaling</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.5690105987521492</v>
+        <v>0.4944341147449103</v>
       </c>
       <c r="D12" t="n">
-        <v>1.760972255264394</v>
+        <v>1.822666281038415</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01443298969072165</v>
+        <v>0.02685950413223141</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1532269257460097</v>
+        <v>0.1120020741124836</v>
       </c>
       <c r="G12" t="n">
-        <v>0.236</v>
+        <v>0.185</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>16/32</t>
+          <t>76/198</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20.95%</t>
+          <t>19.90%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>JAG1;NOTCH1;NOTCH3;NOTCH2;FZD7;DTX1;TCF7L2;HEYL;FZD1;FBXW11;CCND1;SAP30;WNT2;DLL1;FZD5;PRKCA</t>
+          <t>MYO1E;HIPK2;ITGA6;TNFSF11;ADAM19;UCK2;IL1R2;CDCP1;LIF;IGF1R;POU2F1;IGF2R;PHLDA1;HUWE1;AHNAK;BCL2;NCOA3;SYT11;IL18R1;RORA;FURIN;HK2;IRF6;BMPR2;ENPP1;SLC2A3;GABARAPL1;MXD1;PLEC;TNFRSF21;ITGAV;CYFIP1;LCLAT1;CKAP4;BMP2;TWSG1;SNX9;EMP1;MYC;PNP;NCS1;F2RL2;CCND2;COL6A1;PTCH1;ODC1;SPRY4;ITIH5;IKZF4;PRKCH;SCN9A;TIAM1;CDC6;RHOH;CASP3;MAFF;PLAGL1;SWAP70;DENND5A;ABCB1;P4HA1;RGS16;IL2RA;IL2RB;ETFBKMT;KLF6;TGM2;CA2;IKZF2;CD44;SELP;GBP4;LRIG1;SPRED2;IL4R;NOP2</t>
         </is>
       </c>
     </row>
@@ -950,37 +950,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Angiogenesis</t>
+          <t>Notch Signaling</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6060980353037855</v>
+        <v>0.5690105987521472</v>
       </c>
       <c r="D13" t="n">
-        <v>1.749279614783765</v>
+        <v>1.808003353260597</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01470588235294118</v>
+        <v>0.01844262295081967</v>
       </c>
       <c r="F13" t="n">
-        <v>0.149618320610687</v>
+        <v>0.1127724587492361</v>
       </c>
       <c r="G13" t="n">
-        <v>0.248</v>
+        <v>0.197</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>16/36</t>
+          <t>16/32</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10.85%</t>
+          <t>20.95%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>COL5A2;VCAN;STC1;JAG1;POSTN;FGFR1;COL3A1;VAV2;TNFRSF21;ITGAV;THBD;FSTL1;SERPINA5;CCND2;MSX1;PDGFA</t>
+          <t>JAG1;NOTCH1;NOTCH3;NOTCH2;FZD7;DTX1;TCF7L2;HEYL;FZD1;FBXW11;CCND1;SAP30;WNT2;DLL1;FZD5;PRKCA</t>
         </is>
       </c>
     </row>
@@ -992,37 +992,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unfolded Protein Response</t>
+          <t>Estrogen Response Late</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4338784223767975</v>
+        <v>0.440509251627634</v>
       </c>
       <c r="D14" t="n">
-        <v>1.745562528745917</v>
+        <v>1.771876344962541</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07936507936507936</v>
+        <v>0.01440329218106996</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1409277745155608</v>
+        <v>0.1260604541109736</v>
       </c>
       <c r="G14" t="n">
-        <v>0.25</v>
+        <v>0.236</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>49/112</t>
+          <t>62/197</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>27.57%</t>
+          <t>14.90%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>STC2;DCP1A;SLC7A5;ERO1A;EDC4;CNOT6;ERN1;HYOU1;CNOT2;EIF2AK3;EIF4E;ATF6;DCTN1;SLC1A4;NOP14;SHC1;NOLC1;MTREX;IGFBP1;FKBP14;EXOC2;DNAJC3;NFYB;CNOT4;MTHFD2;SEC31A;KIF5B;IARS1;SPCS3;SDAD1;HSPA9;EIF4G1;ALDH18A1;PDIA5;XPOT;TATDN2;PDIA6;EDEM1;TARS1;DCP2;SSR1;BAG3;HSP90B1;EIF2S1;CEBPG;SLC30A5;GEMIN4;TUBB2A;WFS1</t>
+          <t>DLG5;CA12;TFF1;ABHD2;SLC24A3;CPE;NRIP1;ATP2B4;FLNB;FARP1;LARGE1;AFF1;LAMC2;SLC26A2;SLC16A1;BCL2;GJB3;RET;TRIM29;KLF4;HR;PLK4;RABEP1;SLC7A5;KLK10;SERPINA3;HSPA4L;STIL;DYNLT3;PDLIM3;FRK;TMPRSS3;SERPINA5;TPBG;SLC1A4;CELSR2;GAL;NCOR2;SORD;JAK1;SCUBE2;ASCL1;MYOF;NPY1R;SCARB1;CCND1;TOP2A;TIAM1;EGR3;KLK11;UGDH;CDC6;CYP26B1;RAB31;TFF3;KIF20A;PRSS23;DNAJC12;JAK2;OPN3;FKBP4;CHPT1</t>
         </is>
       </c>
     </row>
@@ -1034,37 +1034,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Estrogen Response Late</t>
+          <t>Apical Junction</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4405092516276334</v>
+        <v>0.4801889024905733</v>
       </c>
       <c r="D15" t="n">
-        <v>1.741737772347079</v>
+        <v>1.764578847579752</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01221995926680244</v>
+        <v>0.03258655804480651</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1343052287206566</v>
+        <v>0.1216657451328464</v>
       </c>
       <c r="G15" t="n">
-        <v>0.255</v>
+        <v>0.242</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>62/197</t>
+          <t>70/197</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>14.90%</t>
+          <t>16.69%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>DLG5;CA12;TFF1;ABHD2;SLC24A3;CPE;NRIP1;ATP2B4;FLNB;FARP1;LARGE1;AFF1;LAMC2;SLC26A2;SLC16A1;BCL2;GJB3;RET;TRIM29;KLF4;HR;PLK4;RABEP1;SLC7A5;KLK10;SERPINA3;HSPA4L;STIL;DYNLT3;PDLIM3;FRK;TMPRSS3;SERPINA5;TPBG;SLC1A4;CELSR2;GAL;NCOR2;SORD;JAK1;SCUBE2;ASCL1;MYOF;NPY1R;SCARB1;CCND1;TOP2A;TIAM1;EGR3;KLK11;UGDH;CDC6;CYP26B1;RAB31;TFF3;KIF20A;PRSS23;DNAJC12;JAK2;OPN3;FKBP4;CHPT1</t>
+          <t>VCAN;AKT3;JAM3;RASA1;FLNC;ADAMTS5;IRS1;LAMA3;FBN1;ITGA2;NF1;ITGB1;PCDH1;EPB41L2;CDH6;CDH11;MYH10;NECTIN1;LAMC2;MAP3K20;VCL;SLIT2;PPP2R2C;LAMB3;PARD6G;ADAM9;VWF;SHROOM2;TJP1;PARVA;PIK3CB;COL17A1;COL16A1;VAV2;ACTN1;DMP1;NEXN;GNAI1;ADAM23;CD34;VCAM1;ITGB4;PKD1;THY1;ACTG2;CDH8;LIMA1;CD209;SHC1;MMP2;CLDN14;DLG1;FSCN1;CNTN1;SIRPA;TGFBI;BMP1;NLGN3;CD276;MMP9;EGFR;TRO;FYB1;MYH9;PTEN;DSC3;NFASC;TNFRSF11B;NRXN2;NEGR1</t>
         </is>
       </c>
     </row>
@@ -1076,37 +1076,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Apical Junction</t>
+          <t>Wnt-beta Catenin Signaling</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.4801889024905732</v>
+        <v>0.5378904860870695</v>
       </c>
       <c r="D16" t="n">
-        <v>1.72314758025399</v>
+        <v>1.759577683094787</v>
       </c>
       <c r="E16" t="n">
-        <v>0.04081632653061224</v>
+        <v>0.03232323232323232</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1379509843310567</v>
+        <v>0.1168140150743532</v>
       </c>
       <c r="G16" t="n">
-        <v>0.272</v>
+        <v>0.246</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>70/197</t>
+          <t>24/42</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>16.69%</t>
+          <t>26.17%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>VCAN;AKT3;JAM3;RASA1;FLNC;ADAMTS5;IRS1;LAMA3;FBN1;ITGA2;NF1;ITGB1;PCDH1;EPB41L2;CDH6;CDH11;MYH10;NECTIN1;LAMC2;MAP3K20;VCL;SLIT2;PPP2R2C;LAMB3;PARD6G;ADAM9;VWF;SHROOM2;TJP1;PARVA;PIK3CB;COL17A1;COL16A1;VAV2;ACTN1;DMP1;NEXN;GNAI1;ADAM23;CD34;VCAM1;ITGB4;PKD1;THY1;ACTG2;CDH8;LIMA1;CD209;SHC1;MMP2;CLDN14;DLG1;FSCN1;CNTN1;SIRPA;TGFBI;BMP1;NLGN3;CD276;MMP9;EGFR;TRO;FYB1;MYH9;PTEN;DSC3;NFASC;TNFRSF11B;NRXN2;NEGR1</t>
+          <t>JAG1;NOTCH1;NKD1;DKK1;MAML1;GNAI1;NOTCH4;LEF1;ADAM17;FZD1;HEY2;MYC;NCOR2;CCND2;PTCH1;HDAC2;TCF7;DLL1;JAG2;CTNNB1;NUMB;RBPJ;WNT5B;TP53</t>
         </is>
       </c>
     </row>
@@ -1118,37 +1118,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wnt-beta Catenin Signaling</t>
+          <t>KRAS Signaling Up</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5378904860870698</v>
+        <v>0.4995332494095682</v>
       </c>
       <c r="D17" t="n">
-        <v>1.720922782281102</v>
+        <v>1.747115378288713</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02857142857142857</v>
+        <v>0.03285420944558522</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1302932904781036</v>
+        <v>0.1174577306987167</v>
       </c>
       <c r="G17" t="n">
-        <v>0.275</v>
+        <v>0.261</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>24/42</t>
+          <t>90/200</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>26.17%</t>
+          <t>25.38%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>JAG1;NOTCH1;NKD1;DKK1;MAML1;GNAI1;NOTCH4;LEF1;ADAM17;FZD1;HEY2;MYC;NCOR2;CCND2;PTCH1;HDAC2;TCF7;DLL1;JAG2;CTNNB1;NUMB;RBPJ;WNT5B;TP53</t>
+          <t>TRIB2;INHBA;AKAP12;SOX9;ADGRA2;ITGA2;CPE;DNMBP;NIN;AMMECR1;LIF;MTMR10;GFPT2;ANXA10;CCL20;PRDM1;PRKG2;GPRC5B;ANKH;PTGS2;ADGRL4;SPON1;EPB41L3;PTPRR;PRRX1;ANO1;HKDC1;ITGBL1;ETS1;KLF4;CBL;FLT4;CCSER2;SERPINA3;CFH;SATB1;HOXD11;ERO1A;TMEM158;BTBD3;AVL9;ADAM17;USH1C;RELN;PTCD2;MAP7;BMP2;TNFAIP3;STRN;EMP1;MMP10;CCND2;MAP3K1;F2RL1;F13A1;DCBLD2;TSPAN1;PLEK2;USP12;EVI5;GUCY1A1;MMP9;ABCB1;DOCK2;ACE;DUSP6;PLVAP;RGS16;ANGPTL4;HBEGF;PEG3;PLAUR;CA2;IGF2;VWA5A;IL7R;NR1H4;ETV5;TFPI;WNT7A;CMKLR1;KIF5C;IL1B;ALDH1A3;H2BC3;PECAM1;ADAM8;IGFBP3;NRP1;CBR4</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KRAS Signaling Up</t>
+          <t>Unfolded Protein Response</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.4995332494095683</v>
+        <v>0.4338784223767978</v>
       </c>
       <c r="D18" t="n">
-        <v>1.70413899317904</v>
+        <v>1.742439662642455</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02862985685071575</v>
+        <v>0.0607843137254902</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1348805331694751</v>
+        <v>0.1130792182426036</v>
       </c>
       <c r="G18" t="n">
-        <v>0.29</v>
+        <v>0.265</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>90/200</t>
+          <t>49/112</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25.38%</t>
+          <t>27.57%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>TRIB2;INHBA;AKAP12;SOX9;ADGRA2;ITGA2;CPE;DNMBP;NIN;AMMECR1;LIF;MTMR10;GFPT2;ANXA10;CCL20;PRDM1;PRKG2;GPRC5B;ANKH;PTGS2;ADGRL4;SPON1;EPB41L3;PTPRR;PRRX1;ANO1;HKDC1;ITGBL1;ETS1;KLF4;CBL;FLT4;CCSER2;SERPINA3;CFH;SATB1;HOXD11;ERO1A;TMEM158;BTBD3;AVL9;ADAM17;USH1C;RELN;PTCD2;MAP7;BMP2;TNFAIP3;STRN;EMP1;MMP10;CCND2;MAP3K1;F2RL1;F13A1;DCBLD2;TSPAN1;PLEK2;USP12;EVI5;GUCY1A1;MMP9;ABCB1;DOCK2;ACE;DUSP6;PLVAP;RGS16;ANGPTL4;HBEGF;PEG3;PLAUR;CA2;IGF2;VWA5A;IL7R;NR1H4;ETV5;TFPI;WNT7A;CMKLR1;KIF5C;IL1B;ALDH1A3;H2BC3;PECAM1;ADAM8;IGFBP3;NRP1;CBR4</t>
+          <t>STC2;DCP1A;SLC7A5;ERO1A;EDC4;CNOT6;ERN1;HYOU1;CNOT2;EIF2AK3;EIF4E;ATF6;DCTN1;SLC1A4;NOP14;SHC1;NOLC1;MTREX;IGFBP1;FKBP14;EXOC2;DNAJC3;NFYB;CNOT4;MTHFD2;SEC31A;KIF5B;IARS1;SPCS3;SDAD1;HSPA9;EIF4G1;ALDH18A1;PDIA5;XPOT;TATDN2;PDIA6;EDEM1;TARS1;DCP2;SSR1;BAG3;HSP90B1;EIF2S1;CEBPG;SLC30A5;GEMIN4;TUBB2A;WFS1</t>
         </is>
       </c>
     </row>
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.4241604845068762</v>
+        <v>0.4241604845068759</v>
       </c>
       <c r="D19" t="n">
-        <v>1.688773592682303</v>
+        <v>1.708137434560636</v>
       </c>
       <c r="E19" t="n">
-        <v>0.048828125</v>
+        <v>0.048</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1377795634123477</v>
+        <v>0.1267875331024648</v>
       </c>
       <c r="G19" t="n">
-        <v>0.301</v>
+        <v>0.285</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1244,37 +1244,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>p53 Pathway</t>
+          <t>mTORC1 Signaling</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.3805391143413773</v>
+        <v>0.4308883379003162</v>
       </c>
       <c r="D20" t="n">
-        <v>1.594886286121044</v>
+        <v>1.64074687238222</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08151093439363817</v>
+        <v>0.07344632768361582</v>
       </c>
       <c r="F20" t="n">
-        <v>0.200156477976782</v>
+        <v>0.1635492275198079</v>
       </c>
       <c r="G20" t="n">
-        <v>0.404</v>
+        <v>0.344</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>62/199</t>
+          <t>69/199</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>21.45%</t>
+          <t>22.51%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>KIF13B;PITPNC1;CCNK;CDH13;POM121;SERPINB5;SLC7A11;NOTCH1;LIF;PTPN14;PLK2;XPC;FBXW7;F2R;SLC35D1;APAF1;ZMAT3;ELP1;CDK5R1;AEN;WWP1;KLF4;TAX1BP3;SP1;TGFA;MXD1;KLK8;HSPA4L;FOXO3;CCP110;ERCC5;ITGB4;BMP2;MDM2;CDKN2AIP;CCND2;ZNF365;TM7SF3;TP63;KRT17;DGKA;NOL8;PDGFA;RB1;VDR;CYFIP2;IER3;GPX2;PTPRE;RGS16;HBEGF;PPM1D;EPHA2;ADA;JAG2;NHLH2;VWA5A;RNF19B;CDKN1A;NDRG1;CD82;FOS</t>
+          <t>IGFBP5;STC1;EGLN3;CYP51A1;SLC7A11;GSK3B;AK4;NAMPT;SLC2A1;ELOVL6;ATP2A2;HMGCR;VLDLR;PLOD2;ALDOA;LDLR;ACSL3;HK2;SLC2A3;FADS2;PLK1;SLC7A5;GBE1;ERO1A;MLLT11;SLC6A6;ADIPOR2;DHFR;TBK1;SLC1A4;HMGCS1;PNP;MCM2;SORD;NUP205;ACACA;CDC25A;M6PR;MCM4;PDK1;AURKA;TFRC;MTHFD2;GMPS;RRM2;EPRS1;USO1;P4HA1;UNG;HSPA9;GTF2H1;TXNRD1;HSPA4;FADS1;SQLE;CANX;HSPD1;CDKN1A;ACLY;GOT1;EDEM1;LDHA;RDH11;BUB1;PITPNB;SCD;BCAT1;SSR1;BHLHE40</t>
         </is>
       </c>
     </row>
@@ -1286,37 +1286,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>mTORC1 Signaling</t>
+          <t>PI3K/AKT/mTOR  Signaling</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.4308883379003164</v>
+        <v>0.3735711497265075</v>
       </c>
       <c r="D21" t="n">
-        <v>1.585517600707207</v>
+        <v>1.610077117102528</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1181262729124236</v>
+        <v>0.0778688524590164</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1968019284853355</v>
+        <v>0.1747321246689754</v>
       </c>
       <c r="G21" t="n">
-        <v>0.412</v>
+        <v>0.379</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>69/199</t>
+          <t>43/105</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>22.51%</t>
+          <t>32.43%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>IGFBP5;STC1;EGLN3;CYP51A1;SLC7A11;GSK3B;AK4;NAMPT;SLC2A1;ELOVL6;ATP2A2;HMGCR;VLDLR;PLOD2;ALDOA;LDLR;ACSL3;HK2;SLC2A3;FADS2;PLK1;SLC7A5;GBE1;ERO1A;MLLT11;SLC6A6;ADIPOR2;DHFR;TBK1;SLC1A4;HMGCS1;PNP;MCM2;SORD;NUP205;ACACA;CDC25A;M6PR;MCM4;PDK1;AURKA;TFRC;MTHFD2;GMPS;RRM2;EPRS1;USO1;P4HA1;UNG;HSPA9;GTF2H1;TXNRD1;HSPA4;FADS1;SQLE;CANX;HSPD1;CDKN1A;ACLY;GOT1;EDEM1;LDHA;RDH11;BUB1;PITPNB;SCD;BCAT1;SSR1;BHLHE40</t>
+          <t>SMAD2;PRKAA2;GSK3B;PTPN11;SLC2A1;PIKFYVE;PITX2;MAP2K6;RPTOR;PLCB1;MAPK8;RAF1;EIF4E;TBK1;ACACA;RPS6KA3;PDK1;ATF1;TIAM1;ITPR2;EGFR;CAB39;PTEN;GNGT1;AKT1;CAMK4;PRKAR2A;RIPK1;CDKN1A;MAPK9;HSP90B1;MAP2K3;MAP3K7;ACTR2;TRAF2;TSC2;MAPKAP1;YWHAB;PPP2R1B;PRKCB;CDK1;RALB;MAPK1</t>
         </is>
       </c>
     </row>
@@ -1328,37 +1328,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PI3K/AKT/mTOR  Signaling</t>
+          <t>Apical Surface</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.3735711497265082</v>
+        <v>0.4702224762798736</v>
       </c>
       <c r="D22" t="n">
-        <v>1.567589419754601</v>
+        <v>1.562068022697075</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05625</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2017562991448086</v>
+        <v>0.2043127782789629</v>
       </c>
       <c r="G22" t="n">
-        <v>0.432</v>
+        <v>0.433</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>43/105</t>
+          <t>24/44</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>32.43%</t>
+          <t>30.46%</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SMAD2;PRKAA2;GSK3B;PTPN11;SLC2A1;PIKFYVE;PITX2;MAP2K6;RPTOR;PLCB1;MAPK8;RAF1;EIF4E;TBK1;ACACA;RPS6KA3;PDK1;ATF1;TIAM1;ITPR2;EGFR;CAB39;PTEN;GNGT1;AKT1;CAMK4;PRKAR2A;RIPK1;CDKN1A;MAPK9;HSP90B1;MAP2K3;MAP3K7;ACTR2;TRAF2;TSC2;MAPKAP1;YWHAB;PPP2R1B;PRKCB;CDK1;RALB;MAPK1</t>
+          <t>SULF2;ATP8B1;NCOA6;ADAM10;SHROOM2;EFNA5;PCSK9;ADIPOR2;THY1;GAS1;BRCA1;DCBLD2;AFAP1L2;IL2RB;MDGA1;PLAUR;SRPX;NTNG1;APP;GATA3;B4GALT1;LYPD3;PKHD1;RHCG</t>
         </is>
       </c>
     </row>
@@ -1370,37 +1370,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>G2-M Checkpoint</t>
+          <t>p53 Pathway</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.55618168279909</v>
+        <v>0.3805391143413778</v>
       </c>
       <c r="D23" t="n">
-        <v>1.565504184836012</v>
+        <v>1.560677854980726</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1198428290766208</v>
+        <v>0.08879492600422834</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1942510683370466</v>
+        <v>0.1962703013018759</v>
       </c>
       <c r="G23" t="n">
         <v>0.434</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>113/198</t>
+          <t>62/199</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25.68%</t>
+          <t>21.45%</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>STAG1;ATRX;MKI67;SLC7A1;UCK2;KIF20B;CENPF;SLC12A2;WRN;RASAL2;SMAD3;KNL1;MAP3K20;NOTCH2;CENPE;CTCF;PDS5B;FOXN3;NSD2;SMC2;MEIS2;SMC1A;KIF11;CCNT1;LMNB1;EFNA5;PLK4;INCENP;CASP8AP2;PBK;CUL3;SLC38A1;PLK1;SLC7A5;G3BP1;PURA;RACGAP1;STIL;ABL1;CCNA2;POLE;LBR;NUP98;ESPL1;PRMT5;PAFAH1B1;KIF4A;KIF23;HIF1A;EXO1;SMARCC1;MEIS1;E2F3;MYC;RBL1;MCM2;TPX2;NOLC1;NUP50;ODC1;POLQ;CDC27;CDC25A;CHAF1A;TLE3;CCND1;FBXO5;AURKA;TOP2A;HMMR;TMPO;MAD2L1;SYNCRIP;MARCKS;CDC6;BRCA2;KPNB1;SS18;LIG3;CHEK1;SAP30;KIF5B;NEK2;KIF15;FANCC;PTTG3P;HOXC10;KMT5A;CCNB2;ARID4A;HNRNPU;SMC4;RAD54L;TNPO2;YTHDC1;ATF5;SQLE;NDC80;CUL5;BUB1;PRC1;KPNA2;EZH2;RAD23B;MNAT1;E2F2;XPO1;GSPT1;HSPA8;UPF1;CCNF;NUMA1;RBM14</t>
+          <t>KIF13B;PITPNC1;CCNK;CDH13;POM121;SERPINB5;SLC7A11;NOTCH1;LIF;PTPN14;PLK2;XPC;FBXW7;F2R;SLC35D1;APAF1;ZMAT3;ELP1;CDK5R1;AEN;WWP1;KLF4;TAX1BP3;SP1;TGFA;MXD1;KLK8;HSPA4L;FOXO3;CCP110;ERCC5;ITGB4;BMP2;MDM2;CDKN2AIP;CCND2;ZNF365;TM7SF3;TP63;KRT17;DGKA;NOL8;PDGFA;RB1;VDR;CYFIP2;IER3;GPX2;PTPRE;RGS16;HBEGF;PPM1D;EPHA2;ADA;JAG2;NHLH2;VWA5A;RNF19B;CDKN1A;NDRG1;CD82;FOS</t>
         </is>
       </c>
     </row>
@@ -1412,37 +1412,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Apical Surface</t>
+          <t>TNF-alpha Signaling via NF-kB</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.4702224762798735</v>
+        <v>0.4834116790044717</v>
       </c>
       <c r="D24" t="n">
-        <v>1.536825328488916</v>
+        <v>1.54973695907473</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06841046277665996</v>
+        <v>0.1069182389937107</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2084441106084162</v>
+        <v>0.1947939454595375</v>
       </c>
       <c r="G24" t="n">
-        <v>0.455</v>
+        <v>0.444</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>24/44</t>
+          <t>77/198</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30.46%</t>
+          <t>21.45%</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>SULF2;ATP8B1;NCOA6;ADAM10;SHROOM2;EFNA5;PCSK9;ADIPOR2;THY1;GAS1;BRCA1;DCBLD2;AFAP1L2;IL2RB;MDGA1;PLAUR;SRPX;NTNG1;APP;GATA3;B4GALT1;LYPD3;PKHD1;RHCG</t>
+          <t>DUSP4;ATP2B1;SERPINB8;JAG1;INHBA;PDLIM5;NFAT5;PMEPA1;IRS2;LIF;GFPT2;PLK2;SMAD3;NAMPT;PHLDA1;CCL20;LAMB3;F3;PTGS2;FUT4;PDE4B;KLF4;LDLR;SERPINE1;FJX1;SLC2A3;MXD1;REL;ABCA1;TNFAIP6;KYNU;NFKB1;ACKR3;BMP2;TNFAIP3;MYC;ETS2;GEM;FOSL2;F2RL1;CXCL1;CCND1;EGR1;TNC;EGR3;MARCKS;DUSP5;PANX1;MAFF;PLPP3;NR4A2;DENND5A;SERPINB2;IER3;PTPRE;FOSL1;HBEGF;ZBTB10;TNFAIP8;KLF9;ICOSLG;KLF6;PLAUR;CXCL3;EGR2;CD44;B4GALT5;KDM6B;KLF10;NR4A1;IL6;RNF19B;IL7R;CDKN1A;GCH1;KLF2;FOS</t>
         </is>
       </c>
     </row>
@@ -1454,37 +1454,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TNF-alpha Signaling via NF-kB</t>
+          <t>G2-M Checkpoint</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.4834116790044712</v>
+        <v>0.5561816827990907</v>
       </c>
       <c r="D25" t="n">
-        <v>1.528016862940455</v>
+        <v>1.548488273050737</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1122448979591837</v>
+        <v>0.1113207547169811</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2053033346725593</v>
+        <v>0.1879812589122021</v>
       </c>
       <c r="G25" t="n">
-        <v>0.464</v>
+        <v>0.445</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>77/198</t>
+          <t>113/198</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>21.45%</t>
+          <t>25.68%</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>DUSP4;ATP2B1;SERPINB8;JAG1;INHBA;PDLIM5;NFAT5;PMEPA1;IRS2;LIF;GFPT2;PLK2;SMAD3;NAMPT;PHLDA1;CCL20;LAMB3;F3;PTGS2;FUT4;PDE4B;KLF4;LDLR;SERPINE1;FJX1;SLC2A3;MXD1;REL;ABCA1;TNFAIP6;KYNU;NFKB1;ACKR3;BMP2;TNFAIP3;MYC;ETS2;GEM;FOSL2;F2RL1;CXCL1;CCND1;EGR1;TNC;EGR3;MARCKS;DUSP5;PANX1;MAFF;PLPP3;NR4A2;DENND5A;SERPINB2;IER3;PTPRE;FOSL1;HBEGF;ZBTB10;TNFAIP8;KLF9;ICOSLG;KLF6;PLAUR;CXCL3;EGR2;CD44;B4GALT5;KDM6B;KLF10;NR4A1;IL6;RNF19B;IL7R;CDKN1A;GCH1;KLF2;FOS</t>
+          <t>STAG1;ATRX;MKI67;SLC7A1;UCK2;KIF20B;CENPF;SLC12A2;WRN;RASAL2;SMAD3;KNL1;MAP3K20;NOTCH2;CENPE;CTCF;PDS5B;FOXN3;NSD2;SMC2;MEIS2;SMC1A;KIF11;CCNT1;LMNB1;EFNA5;PLK4;INCENP;CASP8AP2;PBK;CUL3;SLC38A1;PLK1;SLC7A5;G3BP1;PURA;RACGAP1;STIL;ABL1;CCNA2;POLE;LBR;NUP98;ESPL1;PRMT5;PAFAH1B1;KIF4A;KIF23;HIF1A;EXO1;SMARCC1;MEIS1;E2F3;MYC;RBL1;MCM2;TPX2;NOLC1;NUP50;ODC1;POLQ;CDC27;CDC25A;CHAF1A;TLE3;CCND1;FBXO5;AURKA;TOP2A;HMMR;TMPO;MAD2L1;SYNCRIP;MARCKS;CDC6;BRCA2;KPNB1;SS18;LIG3;CHEK1;SAP30;KIF5B;NEK2;KIF15;FANCC;PTTG3P;HOXC10;KMT5A;CCNB2;ARID4A;HNRNPU;SMC4;RAD54L;TNPO2;YTHDC1;ATF5;SQLE;NDC80;CUL5;BUB1;PRC1;KPNA2;EZH2;RAD23B;MNAT1;E2F2;XPO1;GSPT1;HSPA8;UPF1;CCNF;NUMA1;RBM14</t>
         </is>
       </c>
     </row>
@@ -1496,37 +1496,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>heme Metabolism</t>
+          <t>Complement</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.3272705141183365</v>
+        <v>0.4039228462334467</v>
       </c>
       <c r="D26" t="n">
-        <v>1.47238916649476</v>
+        <v>1.50830825418562</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1192307692307692</v>
+        <v>0.1022044088176353</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2434519887505022</v>
+        <v>0.2105781218170707</v>
       </c>
       <c r="G26" t="n">
-        <v>0.525</v>
+        <v>0.479</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>64/199</t>
+          <t>52/200</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>24.17%</t>
+          <t>13.89%</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SMOX;SLC7A11;TNRC6B;NUDT4;BMP2K;SLC6A8;CLCN3;SLC2A1;ANK1;BTRC;MOCOS;RANBP10;RNF123;NR3C1;FOXJ2;ARHGEF12;KLF3;SEC14L1;KHNYN;AGPAT4;FOXO3;MARCHF8;EPB41;BACH1;FECH;XK;TNS1;CDC27;XPO7;LRP10;KDM7A;MFHAS1;ELL2;ADD2;NFE2L1;DCAF10;TFRC;TRIM10;IGSF3;GMPS;HBBP1;DAAM1;MARK3;GCLM;GAPVD1;ADD1;USP15;CAST;TSPO2;P4HA2;TFDP2;NNT;CA2;VEZF1;DCUN1D1;RHAG;SLC30A1;E2F2;SPTA1;H4C3;ERMAP;MXI1;MINPP1;LPIN2</t>
+          <t>CDH13;F5;COL4A2;LRP1;ZEB1;USP8;DYRK2;KIF2A;PIK3CA;PRDM4;F3;FN1;ADAM9;HNF4A;ZFPM2;MMP12;CDK5R1;PDGFB;PLA2G4A;SERPINE1;DGKG;NOTCH4;DGKH;CFH;PCSK9;SH2B3;KYNU;RAF1;TNFAIP3;VCPIP1;KLK1;GNB4;CBLB;TIMP2;MMP14;GNG2;XPNPEP1;CXCL1;DOCK9;GPD2;GMFB;PCLO;RNF4;L3MBTL4;DUSP5;CR1;CASP3;MAFF;PREP;USP14;SERPINB2;JAK2</t>
         </is>
       </c>
     </row>
@@ -1538,37 +1538,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Apoptosis</t>
+          <t>heme Metabolism</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.3548924011236375</v>
+        <v>0.3272705141183357</v>
       </c>
       <c r="D27" t="n">
-        <v>1.439822658825292</v>
+        <v>1.452266151898582</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1239130434782609</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2641283184473221</v>
+        <v>0.2512935424730088</v>
       </c>
       <c r="G27" t="n">
-        <v>0.55</v>
+        <v>0.533</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>52/160</t>
+          <t>64/199</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>25.08%</t>
+          <t>24.17%</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>ROCK1;PDGFRB;IGF2R;F2R;ANKH;CREBBP;TGFB2;DNM1L;LEF1;SATB1;MADD;AVPR1A;PLPPR4;SPTAN1;BMP2;BRCA1;BCL2L11;BCL2L2;TIMP2;EMP1;XIAP;CCND2;MMP2;SLC20A1;CCND1;CYLD;DNAJC3;TOP2A;EGR3;CASP3;SMAD7;RNASEL;IER3;FEZ1;ENO2;HGF;TGFBR3;TIMP3;WEE1;ADD1;CASP2;CD44;IL6;CTNNB1;CDKN1A;GCH1;PSEN1;PMAIP1;IL1B;ETF1;APP;VDAC2</t>
+          <t>SMOX;SLC7A11;TNRC6B;NUDT4;BMP2K;SLC6A8;CLCN3;SLC2A1;ANK1;BTRC;MOCOS;RANBP10;RNF123;NR3C1;FOXJ2;ARHGEF12;KLF3;SEC14L1;KHNYN;AGPAT4;FOXO3;MARCHF8;EPB41;BACH1;FECH;XK;TNS1;CDC27;XPO7;LRP10;KDM7A;MFHAS1;ELL2;ADD2;NFE2L1;DCAF10;TFRC;TRIM10;IGSF3;GMPS;HBBP1;DAAM1;MARK3;GCLM;GAPVD1;ADD1;USP15;CAST;TSPO2;P4HA2;TFDP2;NNT;CA2;VEZF1;DCUN1D1;RHAG;SLC30A1;E2F2;SPTA1;H4C3;ERMAP;MXI1;MINPP1;LPIN2</t>
         </is>
       </c>
     </row>
@@ -1580,37 +1580,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Complement</t>
+          <t>Apoptosis</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.4039228462334469</v>
+        <v>0.3548924011236397</v>
       </c>
       <c r="D28" t="n">
-        <v>1.429282676725547</v>
+        <v>1.447223233357264</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1524008350730689</v>
+        <v>0.1377870563674322</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2634882371322709</v>
+        <v>0.2466218510219325</v>
       </c>
       <c r="G28" t="n">
-        <v>0.556</v>
+        <v>0.541</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>52/200</t>
+          <t>52/160</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>13.89%</t>
+          <t>25.08%</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>CDH13;F5;COL4A2;LRP1;ZEB1;USP8;DYRK2;KIF2A;PIK3CA;PRDM4;F3;FN1;ADAM9;HNF4A;ZFPM2;MMP12;CDK5R1;PDGFB;PLA2G4A;SERPINE1;DGKG;NOTCH4;DGKH;CFH;PCSK9;SH2B3;KYNU;RAF1;TNFAIP3;VCPIP1;KLK1;GNB4;CBLB;TIMP2;MMP14;GNG2;XPNPEP1;CXCL1;DOCK9;GPD2;GMFB;PCLO;RNF4;L3MBTL4;DUSP5;CR1;CASP3;MAFF;PREP;USP14;SERPINB2;JAK2</t>
+          <t>ROCK1;PDGFRB;IGF2R;F2R;ANKH;CREBBP;TGFB2;DNM1L;LEF1;SATB1;MADD;AVPR1A;PLPPR4;SPTAN1;BMP2;BRCA1;BCL2L11;BCL2L2;TIMP2;EMP1;XIAP;CCND2;MMP2;SLC20A1;CCND1;CYLD;DNAJC3;TOP2A;EGR3;CASP3;SMAD7;RNASEL;IER3;FEZ1;ENO2;HGF;TGFBR3;TIMP3;WEE1;ADD1;CASP2;CD44;IL6;CTNNB1;CDKN1A;GCH1;PSEN1;PMAIP1;IL1B;ETF1;APP;VDAC2</t>
         </is>
       </c>
     </row>
@@ -1626,19 +1626,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.4501947866263556</v>
+        <v>0.450194786626354</v>
       </c>
       <c r="D29" t="n">
-        <v>1.388013066393753</v>
+        <v>1.39793301209337</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1242603550295858</v>
+        <v>0.1400394477317554</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2927853986110314</v>
+        <v>0.284329074877048</v>
       </c>
       <c r="G29" t="n">
-        <v>0.598</v>
+        <v>0.588</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.3027224655877102</v>
+        <v>0.3027224655877109</v>
       </c>
       <c r="D30" t="n">
-        <v>1.34873674525459</v>
+        <v>1.357640441354462</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1737451737451738</v>
+        <v>0.1588594704684318</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3198625677117247</v>
+        <v>0.3110065256636299</v>
       </c>
       <c r="G30" t="n">
-        <v>0.634</v>
+        <v>0.617</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1710,19 +1710,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.4229959215932794</v>
+        <v>0.4229959215932798</v>
       </c>
       <c r="D31" t="n">
-        <v>1.310912447348467</v>
+        <v>1.327326248634536</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2429718875502008</v>
+        <v>0.2065439672801636</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3467416633186018</v>
+        <v>0.3297779588510898</v>
       </c>
       <c r="G31" t="n">
-        <v>0.669</v>
+        <v>0.646</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1752,19 +1752,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.3526167449401487</v>
+        <v>0.3526167449401486</v>
       </c>
       <c r="D32" t="n">
-        <v>1.277291785889804</v>
+        <v>1.290288256511964</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1930184804928131</v>
+        <v>0.1781970649895178</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3699581383895592</v>
+        <v>0.3564854546290881</v>
       </c>
       <c r="G32" t="n">
-        <v>0.704</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1794,19 +1794,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.3435431502267781</v>
+        <v>0.3435431502267801</v>
       </c>
       <c r="D33" t="n">
-        <v>1.245746554062118</v>
+        <v>1.286873447077759</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2459349593495935</v>
+        <v>0.2172131147540984</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3905785456006429</v>
+        <v>0.3484008963128947</v>
       </c>
       <c r="G33" t="n">
-        <v>0.727</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1836,19 +1836,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.3327802005075035</v>
+        <v>0.3327802005075036</v>
       </c>
       <c r="D34" t="n">
-        <v>1.225834168648604</v>
+        <v>1.247949542082899</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2215447154471545</v>
+        <v>0.2302771855010661</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3999561707878301</v>
+        <v>0.3733995073982851</v>
       </c>
       <c r="G34" t="n">
-        <v>0.734</v>
+        <v>0.72</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1874,37 +1874,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Myc Targets V2</t>
+          <t>Spermatogenesis</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.409095380854316</v>
+        <v>0.3151432726812448</v>
       </c>
       <c r="D35" t="n">
-        <v>1.207136837570758</v>
+        <v>1.17584188262606</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3366733466933868</v>
+        <v>0.263671875</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4073641670408621</v>
+        <v>0.434889099253472</v>
       </c>
       <c r="G35" t="n">
-        <v>0.744</v>
+        <v>0.773</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>17/57</t>
+          <t>40/133</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>21.93%</t>
+          <t>22.20%</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>UTP20;TCOF1;PLK4;HK2;PLK1;MYC;PPRC1;SORD;NOLC1;MCM4;WDR43;UNG;PRMT3;NOP2;HSPD1;RRP12;GRWD1</t>
+          <t>JAM3;MTNR1A;SLC12A2;IDE;ZC3H14;DCC;AGFG1;MTOR;NOS1;HSPA4L;SIRT1;TOPBP1;MAP7;CSNK2A2;STRBP;GPR182;PIAS2;LPIN1;AURKA;NEK2;PRM2;CLPB;ACE;SLC2A5;ADAD1;CCNB2;DNAJB8;NPY5R;ADCYAP1;PAPOLB;CAMK4;PRKAR2A;TLE4;NCAPH;BUB1;NF2;BRAF;EZH2;IL12RB2;GRM8</t>
         </is>
       </c>
     </row>
@@ -1916,37 +1916,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Oxidative Phosphorylation</t>
+          <t>Myc Targets V2</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-0.3114981848962153</v>
+        <v>0.4090953808543158</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.184118571439612</v>
+        <v>1.170638679259206</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3320158102766799</v>
+        <v>0.3473053892215569</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6105137395459976</v>
+        <v>0.4276599831213806</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7702429149797571</v>
+        <v>0.775</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>75/200</t>
+          <t>17/57</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>17.04%</t>
+          <t>21.93%</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ATP5PO;CYB5A;ATP6V0C;NDUFA2;UQCR10;NDUFB8;NDUFS7;NDUFS8;ATP5MG;NDUFB1;MRPS15;POLR2F;MPC1;ATP5MF;TIMM8B;MTRF1;COX5B;ATP5ME;NDUFB7;NDUFB2;UQCR11;ATP6V1F;ECI1;ETFB;PHYH;ATP6V0B;GPX4;ATP5F1D;SURF1;NDUFA3;TIMM10;ECH1;ATP5MC1;BDH2;LDHB;NDUFA9;NDUFA7;MRPL34;ATP5PF;NDUFS6;ATP5PD;NDUFS3;NDUFB6;NDUFB5;SDHA;COX6C;TCIRG1;MRPL11;UQCRQ;COX8A;HTRA2;NDUFA6;NDUFA4;MTRR;NQO2;ATP5F1E;NDUFV1;RHOT2;SDHD;COX7A2;COX6B1;COX7B;NDUFB4;ACAT1;MRPS12;COX4I1;NDUFC2;HSD17B10;CYC1;COX6A1;ACADVL;FDX1;NDUFA1;SDHB;SUCLG1</t>
+          <t>UTP20;TCOF1;PLK4;HK2;PLK1;MYC;PPRC1;SORD;NOLC1;MCM4;WDR43;UNG;PRMT3;NOP2;HSPD1;RRP12;GRWD1</t>
         </is>
       </c>
     </row>
@@ -1958,37 +1958,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Spermatogenesis</t>
+          <t>Oxidative Phosphorylation</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.3151432726812441</v>
+        <v>-0.3114981848962161</v>
       </c>
       <c r="D37" t="n">
-        <v>1.18286983971897</v>
+        <v>-1.167792425586668</v>
       </c>
       <c r="E37" t="n">
-        <v>0.24609375</v>
+        <v>0.3502024291497975</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4219525914021696</v>
+        <v>0.6365743468866627</v>
       </c>
       <c r="G37" t="n">
-        <v>0.76</v>
+        <v>0.8014256619144603</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>40/133</t>
+          <t>75/200</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>22.20%</t>
+          <t>17.04%</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>JAM3;MTNR1A;SLC12A2;IDE;ZC3H14;DCC;AGFG1;MTOR;NOS1;HSPA4L;SIRT1;TOPBP1;MAP7;CSNK2A2;STRBP;GPR182;PIAS2;LPIN1;AURKA;NEK2;PRM2;CLPB;ACE;SLC2A5;ADAD1;CCNB2;DNAJB8;NPY5R;ADCYAP1;PAPOLB;CAMK4;PRKAR2A;TLE4;NCAPH;BUB1;NF2;BRAF;EZH2;IL12RB2;GRM8</t>
+          <t>ATP5PO;CYB5A;ATP6V0C;NDUFA2;UQCR10;NDUFB8;NDUFS7;NDUFS8;ATP5MG;NDUFB1;MRPS15;POLR2F;MPC1;ATP5MF;TIMM8B;MTRF1;COX5B;ATP5ME;NDUFB7;NDUFB2;UQCR11;ATP6V1F;ECI1;ETFB;PHYH;ATP6V0B;GPX4;ATP5F1D;SURF1;NDUFA3;TIMM10;ECH1;ATP5MC1;BDH2;LDHB;NDUFA9;NDUFA7;MRPL34;ATP5PF;NDUFS6;ATP5PD;NDUFS3;NDUFB6;NDUFB5;SDHA;COX6C;TCIRG1;MRPL11;UQCRQ;COX8A;HTRA2;NDUFA6;NDUFA4;MTRR;NQO2;ATP5F1E;NDUFV1;RHOT2;SDHD;COX7A2;COX6B1;COX7B;NDUFB4;ACAT1;MRPS12;COX4I1;NDUFC2;HSD17B10;CYC1;COX6A1;ACADVL;FDX1;NDUFA1;SDHB;SUCLG1</t>
         </is>
       </c>
     </row>
@@ -2004,19 +2004,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.4238244383583994</v>
+        <v>0.4238244383583983</v>
       </c>
       <c r="D38" t="n">
-        <v>1.132185181353252</v>
+        <v>1.134297826484667</v>
       </c>
       <c r="E38" t="n">
-        <v>0.393638170974155</v>
+        <v>0.4394785847299814</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4621936520691041</v>
+        <v>0.454566442588443</v>
       </c>
       <c r="G38" t="n">
-        <v>0.796</v>
+        <v>0.791</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.2829417615793138</v>
+        <v>0.2829417615793141</v>
       </c>
       <c r="D39" t="n">
-        <v>1.116903703982254</v>
+        <v>1.122122675878954</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2865497076023392</v>
+        <v>0.2757201646090535</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4644001172727569</v>
+        <v>0.4547543673231186</v>
       </c>
       <c r="G39" t="n">
-        <v>0.802</v>
+        <v>0.798</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2084,37 +2084,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Adipogenesis</t>
+          <t>IL-6/JAK/STAT3 Signaling</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.2495380677588965</v>
+        <v>0.3481328239608344</v>
       </c>
       <c r="D40" t="n">
-        <v>1.071924699079343</v>
+        <v>1.113036922951242</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3772455089820359</v>
+        <v>0.3676767676767677</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4989702057473939</v>
+        <v>0.4523077912748872</v>
       </c>
       <c r="G40" t="n">
-        <v>0.823</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>28/200</t>
+          <t>27/87</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>11.40%</t>
+          <t>26.03%</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>LAMA4;COL15A1;COL4A1;IDH3A;MYLK;BAZ2A;GPHN;RREB1;SOWAHC;ELOVL6;ALDOA;ENPP2;FZD4;ITSN1;CHUK;GBE1;ABCA1;SSPN;ADCY6;ADIPOR2;GPAT4;G3BP2;ITIH5;SCARB1;DLAT;LPCAT3;GPD2;CCNG2</t>
+          <t>IL1R2;PTPN11;LEPR;PDGFC;IL18R1;CBL;TNFRSF21;CXCL1;ITGA4;IL2RA;IL7;CSF2RB;IL17RA;CXCL3;CD44;IL6;IL4R;IL1R1;STAT3;INHBE;IL1B;STAT1;OSMR;IL13RA1;A2M;IL15RA;ACVRL1</t>
         </is>
       </c>
     </row>
@@ -2126,37 +2126,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IL-6/JAK/STAT3 Signaling</t>
+          <t>Adipogenesis</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.3481328239608319</v>
+        <v>0.2495380677588961</v>
       </c>
       <c r="D41" t="n">
-        <v>1.069360109357589</v>
+        <v>1.04898698034242</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4274028629856851</v>
+        <v>0.3927038626609442</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4887968600302871</v>
+        <v>0.5069495588949653</v>
       </c>
       <c r="G41" t="n">
-        <v>0.823</v>
+        <v>0.835</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>27/87</t>
+          <t>28/200</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>26.03%</t>
+          <t>11.40%</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>IL1R2;PTPN11;LEPR;PDGFC;IL18R1;CBL;TNFRSF21;CXCL1;ITGA4;IL2RA;IL7;CSF2RB;IL17RA;CXCL3;CD44;IL6;IL4R;IL1R1;STAT3;INHBE;IL1B;STAT1;OSMR;IL13RA1;A2M;IL15RA;ACVRL1</t>
+          <t>LAMA4;COL15A1;COL4A1;IDH3A;MYLK;BAZ2A;GPHN;RREB1;SOWAHC;ELOVL6;ALDOA;ENPP2;FZD4;ITSN1;CHUK;GBE1;ABCA1;SSPN;ADCY6;ADIPOR2;GPAT4;G3BP2;ITIH5;SCARB1;DLAT;LPCAT3;GPD2;CCNG2</t>
         </is>
       </c>
     </row>
@@ -2172,19 +2172,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.2734826073460273</v>
+        <v>0.2734826073460279</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9523938955920161</v>
+        <v>0.9457070625387388</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4878542510121457</v>
+        <v>0.5</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6012053033346726</v>
+        <v>0.6057445508250152</v>
       </c>
       <c r="G42" t="n">
-        <v>0.874</v>
+        <v>0.894</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.2853413234080218</v>
+        <v>0.2853413234080227</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9258257985727453</v>
+        <v>0.9194515091100528</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5173824130879345</v>
+        <v>0.5348399246704332</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6154690393830415</v>
+        <v>0.6227367354137995</v>
       </c>
       <c r="G43" t="n">
-        <v>0.883</v>
+        <v>0.902</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2252,37 +2252,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pperoxisome</t>
+          <t>Bile Acid Metabolism</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.2176451883963228</v>
+        <v>0.2336631989613563</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9187790741956181</v>
+        <v>0.9019923958503805</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4951456310679612</v>
+        <v>0.5669642857142857</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6092177007404007</v>
+        <v>0.6258824898873788</v>
       </c>
       <c r="G44" t="n">
-        <v>0.889</v>
+        <v>0.908</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>18/103</t>
+          <t>20/111</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>18.98%</t>
+          <t>15.90%</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>IDE;ABCB4;ACSL4;SLC23A2;ATXN1;SEMA3C;SMARCC1;CTPS1;CLN6;VPS4B;LONP2;TOP2A;DLG4;ABCB1;PEX5;MLYCD;CLN8;FADS1</t>
+          <t>DIO2;BMP6;SLC23A2;NEDD4;ATXN1;PFKM;FADS2;ABCA1;SULT1B1;PEX1;BCAR3;PEX26;LONP2;AR;ABCA6;CYP7B1;GCLM;TFCP2L1;ABCA2;MLYCD</t>
         </is>
       </c>
     </row>
@@ -2294,37 +2294,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bile Acid Metabolism</t>
+          <t>Pperoxisome</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.2336631989613557</v>
+        <v>0.2176451883963238</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9178099318755926</v>
+        <v>0.8983507446942247</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5421686746987951</v>
+        <v>0.5224215246636771</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5960365141506349</v>
+        <v>0.6146015623889676</v>
       </c>
       <c r="G45" t="n">
-        <v>0.89</v>
+        <v>0.909</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>20/111</t>
+          <t>18/103</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>15.90%</t>
+          <t>18.98%</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>DIO2;BMP6;SLC23A2;NEDD4;ATXN1;PFKM;FADS2;ABCA1;SULT1B1;PEX1;BCAR3;PEX26;LONP2;AR;ABCA6;CYP7B1;GCLM;TFCP2L1;ABCA2;MLYCD</t>
+          <t>IDE;ABCB4;ACSL4;SLC23A2;ATXN1;SEMA3C;SMARCC1;CTPS1;CLN6;VPS4B;LONP2;TOP2A;DLG4;ABCB1;PEX5;MLYCD;CLN8;FADS1</t>
         </is>
       </c>
     </row>
@@ -2340,19 +2340,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.201871769918777</v>
+        <v>0.2018717699187792</v>
       </c>
       <c r="D46" t="n">
-        <v>0.837498829290432</v>
+        <v>0.8414311077176543</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6546184738955824</v>
+        <v>0.6207627118644068</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6708060922604916</v>
+        <v>0.6651234282116336</v>
       </c>
       <c r="G46" t="n">
-        <v>0.917</v>
+        <v>0.924</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2382,19 +2382,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.2658174360904329</v>
+        <v>0.2658174360904352</v>
       </c>
       <c r="D47" t="n">
-        <v>0.80838522976704</v>
+        <v>0.817264982919064</v>
       </c>
       <c r="E47" t="n">
-        <v>0.6051587301587301</v>
+        <v>0.6035502958579881</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6839266104191777</v>
+        <v>0.6755483126230732</v>
       </c>
       <c r="G47" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2424,19 +2424,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.1793502138934537</v>
+        <v>0.179350213893455</v>
       </c>
       <c r="D48" t="n">
-        <v>0.7704907659013048</v>
+        <v>0.7613155751681727</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6673427991886409</v>
+        <v>0.6759656652360515</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7089279787587123</v>
+        <v>0.7176596668054239</v>
       </c>
       <c r="G48" t="n">
-        <v>0.93</v>
+        <v>0.945</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2466,19 +2466,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.186316292110023</v>
+        <v>-0.1863162921100234</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.7194169644705189</v>
+        <v>-0.7377757646901625</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6814516129032258</v>
+        <v>0.6613545816733067</v>
       </c>
       <c r="F49" t="n">
-        <v>0.732815611310235</v>
+        <v>0.7161264977411118</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9726720647773279</v>
+        <v>0.9663951120162932</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2508,19 +2508,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.1815826857720542</v>
+        <v>0.1815826857720555</v>
       </c>
       <c r="D50" t="n">
-        <v>0.5357651192465022</v>
+        <v>0.5421009236835387</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7922606924643585</v>
+        <v>0.8441295546558705</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9184924305240932</v>
+        <v>0.9163403735214954</v>
       </c>
       <c r="G50" t="n">
-        <v>0.975</v>
+        <v>0.979</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2550,19 +2550,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.1577185544168286</v>
+        <v>0.1577185544168297</v>
       </c>
       <c r="D51" t="n">
-        <v>0.451005994794019</v>
+        <v>0.4521465516705857</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9043824701195219</v>
+        <v>0.8891129032258065</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9525110486139011</v>
+        <v>0.955591770217967</v>
       </c>
       <c r="G51" t="n">
-        <v>0.981</v>
+        <v>0.984</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
